--- a/data/file_generation/reference/data_209/八年级登分表_202622_res.xlsx
+++ b/data/file_generation/reference/data_209/八年级登分表_202622_res.xlsx
@@ -5803,18 +5803,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2DAE8C6-C6B9-421B-A4C8-1FC3B5151E99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F60E570-7F13-4CC4-9FFF-E740388F5C12}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD906F6-41C5-4A8F-84F1-CFAFE5E0FEBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF96CC0-168A-4A99-86DE-B12D19BB9CF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{582B4EDB-AC0D-425A-8545-5B45F77BF7F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A65B0437-FF86-4964-A3C7-942E2BA0FFE6}"/>
 </file>